--- a/Datos Tesis Upstream/Estructura de Datos/2526-1/Participaciones Estructura de Datos 2526-1.xlsx
+++ b/Datos Tesis Upstream/Estructura de Datos/2526-1/Participaciones Estructura de Datos 2526-1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nelsoncarrillo/Downloads/tesis-prediccion-participacion/Datos Tesis Upstream/Estructura de Datos/2526-1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB04E3D-EEC8-C54F-9FD1-AA32BC30EAFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE3A03C0-2E48-C848-9029-F58C2F7C4546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -216,7 +216,7 @@
     <author>tc={15A711AD-31A2-3544-815E-B77806E32B7E}</author>
   </authors>
   <commentList>
-    <comment ref="W13" authorId="0" shapeId="0" xr:uid="{CE8D7367-E796-CB43-9F2D-C6EF17AD878C}">
+    <comment ref="X13" authorId="0" shapeId="0" xr:uid="{CE8D7367-E796-CB43-9F2D-C6EF17AD878C}">
       <text>
         <r>
           <rPr>
@@ -230,7 +230,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L28" authorId="1" shapeId="0" xr:uid="{52619A6E-202C-9641-AA2B-E494D5280077}">
+    <comment ref="M28" authorId="1" shapeId="0" xr:uid="{52619A6E-202C-9641-AA2B-E494D5280077}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -238,7 +238,7 @@
     Pizarra</t>
       </text>
     </comment>
-    <comment ref="M29" authorId="2" shapeId="0" xr:uid="{08399C04-CA2D-A847-B22B-3C1A763E5900}">
+    <comment ref="N29" authorId="2" shapeId="0" xr:uid="{08399C04-CA2D-A847-B22B-3C1A763E5900}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -246,7 +246,7 @@
     Pizarra</t>
       </text>
     </comment>
-    <comment ref="T29" authorId="3" shapeId="0" xr:uid="{68FDBB96-E8BC-1742-9C03-AFBBCD713130}">
+    <comment ref="U29" authorId="3" shapeId="0" xr:uid="{68FDBB96-E8BC-1742-9C03-AFBBCD713130}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -254,7 +254,7 @@
     Pizarra</t>
       </text>
     </comment>
-    <comment ref="U29" authorId="0" shapeId="0" xr:uid="{8249CE60-37D1-2048-A3CB-280AD30EF8F5}">
+    <comment ref="V29" authorId="0" shapeId="0" xr:uid="{8249CE60-37D1-2048-A3CB-280AD30EF8F5}">
       <text>
         <r>
           <rPr>
@@ -268,7 +268,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X29" authorId="0" shapeId="0" xr:uid="{1DEF16D9-96BD-AF4D-9DFE-EC9342B55BE5}">
+    <comment ref="Y29" authorId="0" shapeId="0" xr:uid="{1DEF16D9-96BD-AF4D-9DFE-EC9342B55BE5}">
       <text>
         <r>
           <rPr>
@@ -282,7 +282,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M31" authorId="4" shapeId="0" xr:uid="{ECA21B30-8344-F149-81B4-29C0E9DAE850}">
+    <comment ref="N31" authorId="4" shapeId="0" xr:uid="{ECA21B30-8344-F149-81B4-29C0E9DAE850}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -290,7 +290,7 @@
     Pizarra</t>
       </text>
     </comment>
-    <comment ref="N32" authorId="5" shapeId="0" xr:uid="{C0B31B3B-299A-9440-B9F6-5BF9E3001D22}">
+    <comment ref="O32" authorId="5" shapeId="0" xr:uid="{C0B31B3B-299A-9440-B9F6-5BF9E3001D22}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -298,7 +298,7 @@
     Pizarra</t>
       </text>
     </comment>
-    <comment ref="U32" authorId="0" shapeId="0" xr:uid="{EAADA730-0F36-584E-AD0E-E8546209FBE6}">
+    <comment ref="V32" authorId="0" shapeId="0" xr:uid="{EAADA730-0F36-584E-AD0E-E8546209FBE6}">
       <text>
         <r>
           <rPr>
@@ -312,7 +312,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L36" authorId="6" shapeId="0" xr:uid="{333D5F10-E366-B047-8939-47323E5DE319}">
+    <comment ref="M36" authorId="6" shapeId="0" xr:uid="{333D5F10-E366-B047-8939-47323E5DE319}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -320,7 +320,7 @@
     Pizarra</t>
       </text>
     </comment>
-    <comment ref="T36" authorId="7" shapeId="0" xr:uid="{15A711AD-31A2-3544-815E-B77806E32B7E}">
+    <comment ref="U36" authorId="7" shapeId="0" xr:uid="{15A711AD-31A2-3544-815E-B77806E32B7E}">
       <text>
         <t>[Comentario encadenado]
 Tu versión de Excel te permite leer este comentario encadenado; sin embargo, las ediciones que se apliquen se quitarán si el archivo se abre en una versión más reciente de Excel. Más información: https://go.microsoft.com/fwlink/?linkid=870924
@@ -328,7 +328,7 @@
     Pizarra</t>
       </text>
     </comment>
-    <comment ref="U36" authorId="0" shapeId="0" xr:uid="{E8E6DC99-E46C-7045-AD58-7D10ADDCA6AC}">
+    <comment ref="V36" authorId="0" shapeId="0" xr:uid="{E8E6DC99-E46C-7045-AD58-7D10ADDCA6AC}">
       <text>
         <r>
           <rPr>
@@ -341,7 +341,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="W36" authorId="0" shapeId="0" xr:uid="{CAED4DEF-54D0-7840-9385-10BB8888BAE5}">
+    <comment ref="X36" authorId="0" shapeId="0" xr:uid="{CAED4DEF-54D0-7840-9385-10BB8888BAE5}">
       <text>
         <r>
           <rPr>
@@ -355,7 +355,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="X36" authorId="0" shapeId="0" xr:uid="{E7856BAE-CED7-D14E-A7CD-75E43B24A51C}">
+    <comment ref="Y36" authorId="0" shapeId="0" xr:uid="{E7856BAE-CED7-D14E-A7CD-75E43B24A51C}">
       <text>
         <r>
           <rPr>
@@ -373,7 +373,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="133">
   <si>
     <t>Fernando Torre</t>
   </si>
@@ -1431,6 +1431,9 @@
   <si>
     <t>2526-1</t>
   </si>
+  <si>
+    <t>carnet</t>
+  </si>
 </sst>
 </file>
 
@@ -1439,7 +1442,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="d\ mmm"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1574,6 +1577,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1635,7 +1646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1711,6 +1722,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2014,25 +2031,25 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="L28" dT="2025-11-23T02:14:27.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{52619A6E-202C-9641-AA2B-E494D5280077}">
+  <threadedComment ref="M28" dT="2025-11-23T02:14:27.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{52619A6E-202C-9641-AA2B-E494D5280077}">
     <text>Pizarra</text>
   </threadedComment>
-  <threadedComment ref="M29" dT="2025-11-23T02:11:04.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{08399C04-CA2D-A847-B22B-3C1A763E5900}">
+  <threadedComment ref="N29" dT="2025-11-23T02:11:04.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{08399C04-CA2D-A847-B22B-3C1A763E5900}">
     <text>Pizarra</text>
   </threadedComment>
-  <threadedComment ref="T29" dT="2025-11-23T02:09:27.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{68FDBB96-E8BC-1742-9C03-AFBBCD713130}">
+  <threadedComment ref="U29" dT="2025-11-23T02:09:27.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{68FDBB96-E8BC-1742-9C03-AFBBCD713130}">
     <text>Pizarra</text>
   </threadedComment>
-  <threadedComment ref="M31" dT="2025-11-23T02:12:47.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{ECA21B30-8344-F149-81B4-29C0E9DAE850}">
+  <threadedComment ref="N31" dT="2025-11-23T02:12:47.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{ECA21B30-8344-F149-81B4-29C0E9DAE850}">
     <text>Pizarra</text>
   </threadedComment>
-  <threadedComment ref="N32" dT="2025-11-23T02:11:41.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{C0B31B3B-299A-9440-B9F6-5BF9E3001D22}">
+  <threadedComment ref="O32" dT="2025-11-23T02:11:41.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{C0B31B3B-299A-9440-B9F6-5BF9E3001D22}">
     <text>Pizarra</text>
   </threadedComment>
-  <threadedComment ref="L36" dT="2025-11-23T02:14:54.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{333D5F10-E366-B047-8939-47323E5DE319}">
+  <threadedComment ref="M36" dT="2025-11-23T02:14:54.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{333D5F10-E366-B047-8939-47323E5DE319}">
     <text>Pizarra</text>
   </threadedComment>
-  <threadedComment ref="T36" dT="2025-11-23T02:10:08.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{15A711AD-31A2-3544-815E-B77806E32B7E}">
+  <threadedComment ref="U36" dT="2025-11-23T02:10:08.00" personId="{C926D3C3-FEAD-4F55-894F-6A7EA40DF499}" id="{15A711AD-31A2-3544-815E-B77806E32B7E}">
     <text>Pizarra</text>
   </threadedComment>
 </ThreadedComments>
@@ -21960,14 +21977,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AB38"/>
+  <dimension ref="A1:AC38"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="4" width="16" customWidth="1"/>
-    <col min="5" max="28" width="9" customWidth="1"/>
+    <col min="1" max="5" width="16" customWidth="1"/>
+    <col min="6" max="29" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>109</v>
       </c>
@@ -21975,7 +21992,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:29">
       <c r="A2" t="s">
         <v>110</v>
       </c>
@@ -21983,7 +22000,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:29">
       <c r="A3" t="s">
         <v>111</v>
       </c>
@@ -21991,7 +22008,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:29">
       <c r="A5" s="34" t="s">
         <v>112</v>
       </c>
@@ -22004,134 +22021,138 @@
       <c r="D5" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="E5" s="34" t="s">
+      <c r="E5" s="36" t="s">
+        <v>132</v>
+      </c>
+      <c r="F5" s="34" t="s">
         <v>116</v>
       </c>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34" t="s">
+      <c r="G5" s="34"/>
+      <c r="H5" s="34" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34" t="s">
+      <c r="I5" s="34"/>
+      <c r="J5" s="34" t="s">
         <v>118</v>
       </c>
-      <c r="J5" s="34"/>
-      <c r="K5" s="34" t="s">
+      <c r="K5" s="34"/>
+      <c r="L5" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34" t="s">
+      <c r="M5" s="34"/>
+      <c r="N5" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="N5" s="34"/>
-      <c r="O5" s="34" t="s">
+      <c r="O5" s="34"/>
+      <c r="P5" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34" t="s">
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34" t="s">
         <v>122</v>
       </c>
-      <c r="R5" s="34"/>
-      <c r="S5" s="34" t="s">
+      <c r="S5" s="34"/>
+      <c r="T5" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="T5" s="34"/>
-      <c r="U5" s="34" t="s">
+      <c r="U5" s="34"/>
+      <c r="V5" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="V5" s="34"/>
-      <c r="W5" s="34" t="s">
+      <c r="W5" s="34"/>
+      <c r="X5" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="X5" s="34"/>
-      <c r="Y5" s="34" t="s">
+      <c r="Y5" s="34"/>
+      <c r="Z5" s="34" t="s">
         <v>126</v>
       </c>
-      <c r="Z5" s="34"/>
-      <c r="AA5" s="34" t="s">
+      <c r="AA5" s="34"/>
+      <c r="AB5" s="34" t="s">
         <v>127</v>
       </c>
-      <c r="AB5" s="34"/>
-    </row>
-    <row r="6" spans="1:28">
+      <c r="AC5" s="34"/>
+    </row>
+    <row r="6" spans="1:29">
       <c r="A6" s="34"/>
       <c r="B6" s="34"/>
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="35"/>
+      <c r="F6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="F6" s="32" t="s">
+      <c r="G6" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="G6" s="32" t="s">
+      <c r="H6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="H6" s="32" t="s">
+      <c r="I6" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="I6" s="32" t="s">
+      <c r="J6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="J6" s="32" t="s">
+      <c r="K6" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="K6" s="32" t="s">
+      <c r="L6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="L6" s="32" t="s">
+      <c r="M6" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="M6" s="32" t="s">
+      <c r="N6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="N6" s="32" t="s">
+      <c r="O6" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="O6" s="32" t="s">
+      <c r="P6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="P6" s="32" t="s">
+      <c r="Q6" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="Q6" s="32" t="s">
+      <c r="R6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="R6" s="32" t="s">
+      <c r="S6" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="S6" s="32" t="s">
+      <c r="T6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="T6" s="32" t="s">
+      <c r="U6" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="U6" s="32" t="s">
+      <c r="V6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="V6" s="32" t="s">
+      <c r="W6" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="W6" s="32" t="s">
+      <c r="X6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="X6" s="32" t="s">
+      <c r="Y6" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="Y6" s="32" t="s">
+      <c r="Z6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="Z6" s="32" t="s">
+      <c r="AA6" s="32" t="s">
         <v>129</v>
       </c>
-      <c r="AA6" s="32" t="s">
+      <c r="AB6" s="32" t="s">
         <v>128</v>
       </c>
-      <c r="AB6" s="32" t="s">
+      <c r="AC6" s="32" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="7" spans="1:28" ht="14">
+    <row r="7" spans="1:29" ht="14">
       <c r="A7">
         <v>1</v>
       </c>
@@ -22144,23 +22165,28 @@
       <c r="D7" s="29">
         <v>32050015</v>
       </c>
-      <c r="E7" s="9"/>
+      <c r="E7" s="29" t="inlineStr">
+        <is>
+          <t>20251110442</t>
+        </is>
+      </c>
       <c r="F7" s="9"/>
-      <c r="J7" s="9"/>
+      <c r="G7" s="9"/>
       <c r="K7" s="9"/>
       <c r="L7" s="9"/>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
-      <c r="P7" s="9"/>
-      <c r="S7" s="9"/>
+      <c r="O7" s="9"/>
+      <c r="Q7" s="9"/>
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
-      <c r="W7" s="9"/>
+      <c r="V7" s="9"/>
       <c r="X7" s="9"/>
       <c r="Y7" s="9"/>
-      <c r="AA7" s="9"/>
-    </row>
-    <row r="8" spans="1:28" ht="14">
+      <c r="Z7" s="9"/>
+      <c r="AB7" s="9"/>
+    </row>
+    <row r="8" spans="1:29" ht="14">
       <c r="A8">
         <v>2</v>
       </c>
@@ -22173,25 +22199,30 @@
       <c r="D8" s="30">
         <v>30911705</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="30" t="inlineStr">
+        <is>
+          <t>20241110589</t>
+        </is>
+      </c>
       <c r="F8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="G8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
-      <c r="P8" s="9"/>
-      <c r="S8" s="9">
+      <c r="O8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="T8" s="9">
         <v>1</v>
       </c>
-      <c r="T8" s="9"/>
       <c r="U8" s="9"/>
-      <c r="W8" s="9"/>
+      <c r="V8" s="9"/>
       <c r="X8" s="9"/>
       <c r="Y8" s="9"/>
-      <c r="AA8" s="9"/>
-    </row>
-    <row r="9" spans="1:28" ht="14">
+      <c r="Z8" s="9"/>
+      <c r="AB8" s="9"/>
+    </row>
+    <row r="9" spans="1:29" ht="14">
       <c r="A9">
         <v>3</v>
       </c>
@@ -22204,23 +22235,28 @@
       <c r="D9" s="29">
         <v>30906782</v>
       </c>
-      <c r="E9" s="9"/>
+      <c r="E9" s="29" t="inlineStr">
+        <is>
+          <t>20241110456</t>
+        </is>
+      </c>
       <c r="F9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="G9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
       <c r="N9" s="9"/>
-      <c r="P9" s="9"/>
-      <c r="S9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="Q9" s="9"/>
       <c r="T9" s="9"/>
       <c r="U9" s="9"/>
-      <c r="W9" s="9"/>
+      <c r="V9" s="9"/>
       <c r="X9" s="9"/>
       <c r="Y9" s="9"/>
-      <c r="AA9" s="9"/>
-    </row>
-    <row r="10" spans="1:28" ht="14">
+      <c r="Z9" s="9"/>
+      <c r="AB9" s="9"/>
+    </row>
+    <row r="10" spans="1:29" ht="14">
       <c r="A10">
         <v>4</v>
       </c>
@@ -22233,23 +22269,28 @@
       <c r="D10" s="30">
         <v>31852011</v>
       </c>
-      <c r="E10" s="9"/>
+      <c r="E10" s="30" t="inlineStr">
+        <is>
+          <t>20251120004</t>
+        </is>
+      </c>
       <c r="F10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="G10" s="9"/>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
       <c r="N10" s="9"/>
-      <c r="P10" s="9"/>
-      <c r="S10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="Q10" s="9"/>
       <c r="T10" s="9"/>
       <c r="U10" s="9"/>
-      <c r="W10" s="9"/>
+      <c r="V10" s="9"/>
       <c r="X10" s="9"/>
       <c r="Y10" s="9"/>
-      <c r="AA10" s="9"/>
-    </row>
-    <row r="11" spans="1:28" ht="14">
+      <c r="Z10" s="9"/>
+      <c r="AB10" s="9"/>
+    </row>
+    <row r="11" spans="1:29" ht="14">
       <c r="A11">
         <v>5</v>
       </c>
@@ -22262,23 +22303,28 @@
       <c r="D11" s="29">
         <v>29947503</v>
       </c>
-      <c r="E11" s="9"/>
+      <c r="E11" s="29" t="inlineStr">
+        <is>
+          <t>20221110165</t>
+        </is>
+      </c>
       <c r="F11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="G11" s="9"/>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
       <c r="N11" s="9"/>
-      <c r="P11" s="9"/>
-      <c r="S11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="Q11" s="9"/>
       <c r="T11" s="9"/>
       <c r="U11" s="9"/>
-      <c r="W11" s="9"/>
+      <c r="V11" s="9"/>
       <c r="X11" s="9"/>
       <c r="Y11" s="9"/>
-      <c r="AA11" s="9"/>
-    </row>
-    <row r="12" spans="1:28" ht="14">
+      <c r="Z11" s="9"/>
+      <c r="AB11" s="9"/>
+    </row>
+    <row r="12" spans="1:29" ht="14">
       <c r="A12">
         <v>6</v>
       </c>
@@ -22291,29 +22337,34 @@
       <c r="D12" s="30">
         <v>31448284</v>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="9">
+      <c r="E12" s="30" t="inlineStr">
+        <is>
+          <t>20231120166</t>
+        </is>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="G12" s="9">
         <v>1</v>
       </c>
-      <c r="J12" s="9"/>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
       <c r="N12" s="9"/>
-      <c r="P12" s="9"/>
-      <c r="S12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="Q12" s="9"/>
       <c r="T12" s="9"/>
       <c r="U12" s="9"/>
-      <c r="W12" s="9"/>
+      <c r="V12" s="9"/>
       <c r="X12" s="9"/>
-      <c r="Y12" s="9">
+      <c r="Y12" s="9"/>
+      <c r="Z12" s="9">
         <v>1</v>
       </c>
-      <c r="AA12" s="9">
+      <c r="AB12" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:28" ht="14">
+    <row r="13" spans="1:29" ht="14">
       <c r="A13">
         <v>7</v>
       </c>
@@ -22326,25 +22377,30 @@
       <c r="D13" s="29">
         <v>30693530</v>
       </c>
-      <c r="E13" s="9"/>
+      <c r="E13" s="29" t="inlineStr">
+        <is>
+          <t>20241110374</t>
+        </is>
+      </c>
       <c r="F13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="G13" s="9"/>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
       <c r="N13" s="9"/>
-      <c r="P13" s="9"/>
-      <c r="S13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="Q13" s="9"/>
       <c r="T13" s="9"/>
       <c r="U13" s="9"/>
-      <c r="W13" s="9">
+      <c r="V13" s="9"/>
+      <c r="X13" s="9">
         <v>6</v>
       </c>
-      <c r="X13" s="9"/>
       <c r="Y13" s="9"/>
-      <c r="AA13" s="9"/>
-    </row>
-    <row r="14" spans="1:28" ht="14">
+      <c r="Z13" s="9"/>
+      <c r="AB13" s="9"/>
+    </row>
+    <row r="14" spans="1:29" ht="14">
       <c r="A14">
         <v>8</v>
       </c>
@@ -22357,23 +22413,28 @@
       <c r="D14" s="30">
         <v>28175373</v>
       </c>
-      <c r="E14" s="9"/>
+      <c r="E14" s="30" t="inlineStr">
+        <is>
+          <t>20201110335</t>
+        </is>
+      </c>
       <c r="F14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="G14" s="9"/>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
       <c r="N14" s="9"/>
-      <c r="P14" s="9"/>
-      <c r="S14" s="9"/>
+      <c r="O14" s="9"/>
+      <c r="Q14" s="9"/>
       <c r="T14" s="9"/>
       <c r="U14" s="9"/>
-      <c r="W14" s="9"/>
+      <c r="V14" s="9"/>
       <c r="X14" s="9"/>
       <c r="Y14" s="9"/>
-      <c r="AA14" s="9"/>
-    </row>
-    <row r="15" spans="1:28" ht="14">
+      <c r="Z14" s="9"/>
+      <c r="AB14" s="9"/>
+    </row>
+    <row r="15" spans="1:29" ht="14">
       <c r="A15">
         <v>9</v>
       </c>
@@ -22386,27 +22447,32 @@
       <c r="D15" s="29">
         <v>31792509</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="29" t="inlineStr">
+        <is>
+          <t>20251110112</t>
+        </is>
+      </c>
+      <c r="F15" s="9">
         <v>1</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9">
+      <c r="G15" s="9"/>
+      <c r="K15" s="9"/>
+      <c r="L15" s="9">
         <v>1</v>
       </c>
-      <c r="L15" s="9"/>
       <c r="M15" s="9"/>
       <c r="N15" s="9"/>
-      <c r="P15" s="9"/>
-      <c r="S15" s="9"/>
+      <c r="O15" s="9"/>
+      <c r="Q15" s="9"/>
       <c r="T15" s="9"/>
       <c r="U15" s="9"/>
-      <c r="W15" s="9"/>
+      <c r="V15" s="9"/>
       <c r="X15" s="9"/>
       <c r="Y15" s="9"/>
-      <c r="AA15" s="9"/>
-    </row>
-    <row r="16" spans="1:28" ht="14">
+      <c r="Z15" s="9"/>
+      <c r="AB15" s="9"/>
+    </row>
+    <row r="16" spans="1:29" ht="14">
       <c r="A16">
         <v>10</v>
       </c>
@@ -22419,23 +22485,28 @@
       <c r="D16" s="30">
         <v>30942903</v>
       </c>
-      <c r="E16" s="9"/>
+      <c r="E16" s="30" t="inlineStr">
+        <is>
+          <t>20241120119</t>
+        </is>
+      </c>
       <c r="F16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="G16" s="9"/>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
       <c r="N16" s="9"/>
-      <c r="P16" s="9"/>
-      <c r="S16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="Q16" s="9"/>
       <c r="T16" s="9"/>
       <c r="U16" s="9"/>
-      <c r="W16" s="9"/>
+      <c r="V16" s="9"/>
       <c r="X16" s="9"/>
       <c r="Y16" s="9"/>
-      <c r="AA16" s="9"/>
-    </row>
-    <row r="17" spans="1:27" ht="14">
+      <c r="Z16" s="9"/>
+      <c r="AB16" s="9"/>
+    </row>
+    <row r="17" spans="1:28" ht="14">
       <c r="A17">
         <v>11</v>
       </c>
@@ -22448,23 +22519,28 @@
       <c r="D17" s="29">
         <v>31307971</v>
       </c>
-      <c r="E17" s="9"/>
+      <c r="E17" s="29" t="inlineStr">
+        <is>
+          <t>20241110377</t>
+        </is>
+      </c>
       <c r="F17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="G17" s="9"/>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
       <c r="N17" s="9"/>
-      <c r="P17" s="9"/>
-      <c r="S17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="Q17" s="9"/>
       <c r="T17" s="9"/>
       <c r="U17" s="9"/>
-      <c r="W17" s="9"/>
+      <c r="V17" s="9"/>
       <c r="X17" s="9"/>
       <c r="Y17" s="9"/>
-      <c r="AA17" s="9"/>
-    </row>
-    <row r="18" spans="1:27" ht="14">
+      <c r="Z17" s="9"/>
+      <c r="AB17" s="9"/>
+    </row>
+    <row r="18" spans="1:28" ht="14">
       <c r="A18">
         <v>12</v>
       </c>
@@ -22477,23 +22553,28 @@
       <c r="D18" s="30">
         <v>29948233</v>
       </c>
-      <c r="E18" s="9"/>
+      <c r="E18" s="30" t="inlineStr">
+        <is>
+          <t>20241110472</t>
+        </is>
+      </c>
       <c r="F18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="G18" s="9"/>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
       <c r="N18" s="9"/>
-      <c r="P18" s="9"/>
-      <c r="S18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="Q18" s="9"/>
       <c r="T18" s="9"/>
       <c r="U18" s="9"/>
-      <c r="W18" s="9"/>
+      <c r="V18" s="9"/>
       <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
-      <c r="AA18" s="9"/>
-    </row>
-    <row r="19" spans="1:27" ht="14">
+      <c r="Z18" s="9"/>
+      <c r="AB18" s="9"/>
+    </row>
+    <row r="19" spans="1:28" ht="14">
       <c r="A19">
         <v>13</v>
       </c>
@@ -22506,23 +22587,28 @@
       <c r="D19" s="29">
         <v>31886469</v>
       </c>
-      <c r="E19" s="9"/>
+      <c r="E19" s="29" t="inlineStr">
+        <is>
+          <t>20251110136</t>
+        </is>
+      </c>
       <c r="F19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="G19" s="9"/>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
       <c r="N19" s="9"/>
-      <c r="P19" s="9"/>
-      <c r="S19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="Q19" s="9"/>
       <c r="T19" s="9"/>
       <c r="U19" s="9"/>
-      <c r="W19" s="9"/>
+      <c r="V19" s="9"/>
       <c r="X19" s="9"/>
       <c r="Y19" s="9"/>
-      <c r="AA19" s="9"/>
-    </row>
-    <row r="20" spans="1:27" ht="14">
+      <c r="Z19" s="9"/>
+      <c r="AB19" s="9"/>
+    </row>
+    <row r="20" spans="1:28" ht="14">
       <c r="A20">
         <v>14</v>
       </c>
@@ -22535,23 +22621,28 @@
       <c r="D20" s="30">
         <v>26794618</v>
       </c>
-      <c r="E20" s="9"/>
+      <c r="E20" s="30" t="inlineStr">
+        <is>
+          <t>20171130051</t>
+        </is>
+      </c>
       <c r="F20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="G20" s="9"/>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
       <c r="N20" s="9"/>
-      <c r="P20" s="9"/>
-      <c r="S20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="Q20" s="9"/>
       <c r="T20" s="9"/>
       <c r="U20" s="9"/>
-      <c r="W20" s="9"/>
+      <c r="V20" s="9"/>
       <c r="X20" s="9"/>
       <c r="Y20" s="9"/>
-      <c r="AA20" s="9"/>
-    </row>
-    <row r="21" spans="1:27" ht="14">
+      <c r="Z20" s="9"/>
+      <c r="AB20" s="9"/>
+    </row>
+    <row r="21" spans="1:28" ht="14">
       <c r="A21">
         <v>15</v>
       </c>
@@ -22564,23 +22655,28 @@
       <c r="D21" s="29">
         <v>30245943</v>
       </c>
-      <c r="E21" s="9"/>
+      <c r="E21" s="29" t="inlineStr">
+        <is>
+          <t>20231110360</t>
+        </is>
+      </c>
       <c r="F21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="G21" s="9"/>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
       <c r="N21" s="9"/>
-      <c r="P21" s="9"/>
-      <c r="S21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="Q21" s="9"/>
       <c r="T21" s="9"/>
       <c r="U21" s="9"/>
-      <c r="W21" s="9"/>
+      <c r="V21" s="9"/>
       <c r="X21" s="9"/>
       <c r="Y21" s="9"/>
-      <c r="AA21" s="9"/>
-    </row>
-    <row r="22" spans="1:27" ht="14">
+      <c r="Z21" s="9"/>
+      <c r="AB21" s="9"/>
+    </row>
+    <row r="22" spans="1:28" ht="14">
       <c r="A22">
         <v>16</v>
       </c>
@@ -22593,29 +22689,34 @@
       <c r="D22" s="30">
         <v>31229787</v>
       </c>
-      <c r="E22" s="9"/>
-      <c r="F22" s="9">
+      <c r="E22" s="30" t="inlineStr">
+        <is>
+          <t>20241110455</t>
+        </is>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9">
         <v>1</v>
       </c>
-      <c r="J22" s="9">
+      <c r="K22" s="9">
         <v>1</v>
       </c>
-      <c r="K22" s="9"/>
       <c r="L22" s="9"/>
-      <c r="M22" s="9">
+      <c r="M22" s="9"/>
+      <c r="N22" s="9">
         <v>3</v>
       </c>
-      <c r="N22" s="9"/>
-      <c r="P22" s="9"/>
-      <c r="S22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="Q22" s="9"/>
       <c r="T22" s="9"/>
       <c r="U22" s="9"/>
-      <c r="W22" s="9"/>
+      <c r="V22" s="9"/>
       <c r="X22" s="9"/>
       <c r="Y22" s="9"/>
-      <c r="AA22" s="9"/>
-    </row>
-    <row r="23" spans="1:27" ht="14">
+      <c r="Z22" s="9"/>
+      <c r="AB22" s="9"/>
+    </row>
+    <row r="23" spans="1:28" ht="14">
       <c r="A23">
         <v>17</v>
       </c>
@@ -22628,23 +22729,28 @@
       <c r="D23" s="29">
         <v>30719195</v>
       </c>
-      <c r="E23" s="9"/>
+      <c r="E23" s="29" t="inlineStr">
+        <is>
+          <t>20231110418</t>
+        </is>
+      </c>
       <c r="F23" s="9"/>
-      <c r="J23" s="9"/>
+      <c r="G23" s="9"/>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
-      <c r="P23" s="9"/>
-      <c r="S23" s="9"/>
+      <c r="O23" s="9"/>
+      <c r="Q23" s="9"/>
       <c r="T23" s="9"/>
       <c r="U23" s="9"/>
-      <c r="W23" s="9"/>
+      <c r="V23" s="9"/>
       <c r="X23" s="9"/>
       <c r="Y23" s="9"/>
-      <c r="AA23" s="9"/>
-    </row>
-    <row r="24" spans="1:27" ht="14">
+      <c r="Z23" s="9"/>
+      <c r="AB23" s="9"/>
+    </row>
+    <row r="24" spans="1:28" ht="14">
       <c r="A24">
         <v>18</v>
       </c>
@@ -22657,23 +22763,28 @@
       <c r="D24" s="30">
         <v>31785756</v>
       </c>
-      <c r="E24" s="9"/>
+      <c r="E24" s="30" t="inlineStr">
+        <is>
+          <t>20241130167</t>
+        </is>
+      </c>
       <c r="F24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="G24" s="9"/>
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
       <c r="N24" s="9"/>
-      <c r="P24" s="9"/>
-      <c r="S24" s="9"/>
+      <c r="O24" s="9"/>
+      <c r="Q24" s="9"/>
       <c r="T24" s="9"/>
       <c r="U24" s="9"/>
-      <c r="W24" s="9"/>
+      <c r="V24" s="9"/>
       <c r="X24" s="9"/>
       <c r="Y24" s="9"/>
-      <c r="AA24" s="9"/>
-    </row>
-    <row r="25" spans="1:27" ht="14">
+      <c r="Z24" s="9"/>
+      <c r="AB24" s="9"/>
+    </row>
+    <row r="25" spans="1:28" ht="14">
       <c r="A25">
         <v>19</v>
       </c>
@@ -22686,23 +22797,28 @@
       <c r="D25" s="29">
         <v>31020400</v>
       </c>
-      <c r="E25" s="9"/>
+      <c r="E25" s="29" t="inlineStr">
+        <is>
+          <t>20231130043</t>
+        </is>
+      </c>
       <c r="F25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="G25" s="9"/>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
       <c r="N25" s="9"/>
-      <c r="P25" s="9"/>
-      <c r="S25" s="9"/>
+      <c r="O25" s="9"/>
+      <c r="Q25" s="9"/>
       <c r="T25" s="9"/>
       <c r="U25" s="9"/>
-      <c r="W25" s="9"/>
+      <c r="V25" s="9"/>
       <c r="X25" s="9"/>
       <c r="Y25" s="9"/>
-      <c r="AA25" s="9"/>
-    </row>
-    <row r="26" spans="1:27" ht="14">
+      <c r="Z25" s="9"/>
+      <c r="AB25" s="9"/>
+    </row>
+    <row r="26" spans="1:28" ht="14">
       <c r="A26">
         <v>20</v>
       </c>
@@ -22715,23 +22831,28 @@
       <c r="D26" s="30">
         <v>29611077</v>
       </c>
-      <c r="E26" s="9"/>
+      <c r="E26" s="30" t="inlineStr">
+        <is>
+          <t>20221110015</t>
+        </is>
+      </c>
       <c r="F26" s="9"/>
-      <c r="J26" s="9"/>
+      <c r="G26" s="9"/>
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
       <c r="M26" s="9"/>
       <c r="N26" s="9"/>
-      <c r="P26" s="9"/>
-      <c r="S26" s="9"/>
+      <c r="O26" s="9"/>
+      <c r="Q26" s="9"/>
       <c r="T26" s="9"/>
       <c r="U26" s="9"/>
-      <c r="W26" s="9"/>
+      <c r="V26" s="9"/>
       <c r="X26" s="9"/>
       <c r="Y26" s="9"/>
-      <c r="AA26" s="9"/>
-    </row>
-    <row r="27" spans="1:27" ht="14">
+      <c r="Z26" s="9"/>
+      <c r="AB26" s="9"/>
+    </row>
+    <row r="27" spans="1:28" ht="14">
       <c r="A27">
         <v>21</v>
       </c>
@@ -22744,25 +22865,30 @@
       <c r="D27" s="29">
         <v>31587327</v>
       </c>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9">
+      <c r="E27" s="29" t="inlineStr">
+        <is>
+          <t>20241130168</t>
+        </is>
+      </c>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9">
         <v>1</v>
       </c>
-      <c r="J27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
       <c r="N27" s="9"/>
-      <c r="P27" s="9"/>
-      <c r="S27" s="9"/>
+      <c r="O27" s="9"/>
+      <c r="Q27" s="9"/>
       <c r="T27" s="9"/>
       <c r="U27" s="9"/>
-      <c r="W27" s="9"/>
+      <c r="V27" s="9"/>
       <c r="X27" s="9"/>
       <c r="Y27" s="9"/>
-      <c r="AA27" s="9"/>
-    </row>
-    <row r="28" spans="1:27" ht="14">
+      <c r="Z27" s="9"/>
+      <c r="AB27" s="9"/>
+    </row>
+    <row r="28" spans="1:28" ht="14">
       <c r="A28">
         <v>22</v>
       </c>
@@ -22775,25 +22901,30 @@
       <c r="D28" s="30">
         <v>30229939</v>
       </c>
-      <c r="E28" s="9"/>
+      <c r="E28" s="30" t="inlineStr">
+        <is>
+          <t>20221120020</t>
+        </is>
+      </c>
       <c r="F28" s="9"/>
-      <c r="J28" s="9"/>
+      <c r="G28" s="9"/>
       <c r="K28" s="9"/>
-      <c r="L28" s="9">
+      <c r="L28" s="9"/>
+      <c r="M28" s="9">
         <v>4</v>
       </c>
-      <c r="M28" s="9"/>
       <c r="N28" s="9"/>
-      <c r="P28" s="9"/>
-      <c r="S28" s="9"/>
+      <c r="O28" s="9"/>
+      <c r="Q28" s="9"/>
       <c r="T28" s="9"/>
       <c r="U28" s="9"/>
-      <c r="W28" s="9"/>
+      <c r="V28" s="9"/>
       <c r="X28" s="9"/>
       <c r="Y28" s="9"/>
-      <c r="AA28" s="9"/>
-    </row>
-    <row r="29" spans="1:27" ht="14">
+      <c r="Z28" s="9"/>
+      <c r="AB28" s="9"/>
+    </row>
+    <row r="29" spans="1:28" ht="14">
       <c r="A29">
         <v>23</v>
       </c>
@@ -22806,43 +22937,48 @@
       <c r="D29" s="29">
         <v>27985520</v>
       </c>
-      <c r="E29" s="9">
-        <v>1</v>
+      <c r="E29" s="29" t="inlineStr">
+        <is>
+          <t>20201110250</t>
+        </is>
       </c>
       <c r="F29" s="9">
         <v>1</v>
       </c>
-      <c r="J29" s="9">
+      <c r="G29" s="9">
         <v>1</v>
       </c>
-      <c r="K29" s="9"/>
+      <c r="K29" s="9">
+        <v>1</v>
+      </c>
       <c r="L29" s="9"/>
-      <c r="M29" s="9">
+      <c r="M29" s="9"/>
+      <c r="N29" s="9">
         <v>8</v>
       </c>
-      <c r="N29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="S29" s="9">
+      <c r="O29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="T29" s="9">
         <v>1</v>
       </c>
-      <c r="T29" s="9">
+      <c r="U29" s="9">
         <v>2</v>
       </c>
-      <c r="U29" s="9">
+      <c r="V29" s="9">
         <v>4</v>
       </c>
-      <c r="W29" s="9"/>
-      <c r="X29" s="9">
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9">
         <v>3</v>
       </c>
-      <c r="Y29" s="9">
+      <c r="Z29" s="9">
         <v>1</v>
       </c>
-      <c r="AA29" s="9">
+      <c r="AB29" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="14">
+    <row r="30" spans="1:28" ht="14">
       <c r="A30">
         <v>24</v>
       </c>
@@ -22855,23 +22991,28 @@
       <c r="D30" s="30">
         <v>31623487</v>
       </c>
-      <c r="E30" s="9"/>
+      <c r="E30" s="30" t="inlineStr">
+        <is>
+          <t>20231110186</t>
+        </is>
+      </c>
       <c r="F30" s="9"/>
-      <c r="J30" s="9"/>
+      <c r="G30" s="9"/>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
       <c r="N30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="S30" s="9"/>
+      <c r="O30" s="9"/>
+      <c r="Q30" s="9"/>
       <c r="T30" s="9"/>
       <c r="U30" s="9"/>
-      <c r="W30" s="9"/>
+      <c r="V30" s="9"/>
       <c r="X30" s="9"/>
       <c r="Y30" s="9"/>
-      <c r="AA30" s="9"/>
-    </row>
-    <row r="31" spans="1:27" ht="14">
+      <c r="Z30" s="9"/>
+      <c r="AB30" s="9"/>
+    </row>
+    <row r="31" spans="1:28" ht="14">
       <c r="A31">
         <v>25</v>
       </c>
@@ -22884,29 +23025,34 @@
       <c r="D31" s="29">
         <v>27714324</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="29" t="inlineStr">
+        <is>
+          <t>20241130162</t>
+        </is>
+      </c>
+      <c r="F31" s="9">
         <v>2</v>
       </c>
-      <c r="F31" s="9">
+      <c r="G31" s="9">
         <v>1</v>
       </c>
-      <c r="J31" s="9"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
-      <c r="M31" s="9">
+      <c r="M31" s="9"/>
+      <c r="N31" s="9">
         <v>3</v>
       </c>
-      <c r="N31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="S31" s="9"/>
+      <c r="O31" s="9"/>
+      <c r="Q31" s="9"/>
       <c r="T31" s="9"/>
       <c r="U31" s="9"/>
-      <c r="W31" s="9"/>
+      <c r="V31" s="9"/>
       <c r="X31" s="9"/>
       <c r="Y31" s="9"/>
-      <c r="AA31" s="9"/>
-    </row>
-    <row r="32" spans="1:27" ht="14">
+      <c r="Z31" s="9"/>
+      <c r="AB31" s="9"/>
+    </row>
+    <row r="32" spans="1:28" ht="14">
       <c r="A32">
         <v>26</v>
       </c>
@@ -22919,35 +23065,40 @@
       <c r="D32" s="30">
         <v>32001374</v>
       </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9">
+      <c r="E32" s="30" t="inlineStr">
+        <is>
+          <t>20251110189</t>
+        </is>
+      </c>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9">
         <v>2</v>
       </c>
-      <c r="J32" s="9">
+      <c r="K32" s="9">
         <v>1</v>
       </c>
-      <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
-      <c r="N32" s="9">
+      <c r="N32" s="9"/>
+      <c r="O32" s="9">
         <v>5</v>
       </c>
-      <c r="P32" s="9">
+      <c r="Q32" s="9">
         <v>1</v>
       </c>
-      <c r="S32" s="9">
+      <c r="T32" s="9">
         <v>1</v>
       </c>
-      <c r="T32" s="9"/>
-      <c r="U32" s="9">
+      <c r="U32" s="9"/>
+      <c r="V32" s="9">
         <v>4</v>
       </c>
-      <c r="W32" s="9"/>
       <c r="X32" s="9"/>
       <c r="Y32" s="9"/>
-      <c r="AA32" s="9"/>
-    </row>
-    <row r="33" spans="1:27" ht="14">
+      <c r="Z32" s="9"/>
+      <c r="AB32" s="9"/>
+    </row>
+    <row r="33" spans="1:28" ht="14">
       <c r="A33">
         <v>27</v>
       </c>
@@ -22960,27 +23111,32 @@
       <c r="D33" s="29">
         <v>30394855</v>
       </c>
-      <c r="E33" s="9">
-        <v>1</v>
+      <c r="E33" s="29" t="inlineStr">
+        <is>
+          <t>20241110467</t>
+        </is>
       </c>
       <c r="F33" s="9">
         <v>1</v>
       </c>
-      <c r="J33" s="9"/>
+      <c r="G33" s="9">
+        <v>1</v>
+      </c>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
-      <c r="P33" s="9"/>
-      <c r="S33" s="9"/>
+      <c r="O33" s="9"/>
+      <c r="Q33" s="9"/>
       <c r="T33" s="9"/>
       <c r="U33" s="9"/>
-      <c r="W33" s="9"/>
+      <c r="V33" s="9"/>
       <c r="X33" s="9"/>
       <c r="Y33" s="9"/>
-      <c r="AA33" s="9"/>
-    </row>
-    <row r="34" spans="1:27" ht="14">
+      <c r="Z33" s="9"/>
+      <c r="AB33" s="9"/>
+    </row>
+    <row r="34" spans="1:28" ht="14">
       <c r="A34">
         <v>28</v>
       </c>
@@ -22993,27 +23149,32 @@
       <c r="D34" s="30">
         <v>31872806</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="30" t="inlineStr">
+        <is>
+          <t>20251110273</t>
+        </is>
+      </c>
+      <c r="F34" s="9">
         <v>1</v>
       </c>
-      <c r="F34" s="9"/>
-      <c r="J34" s="9"/>
+      <c r="G34" s="9"/>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
-      <c r="P34" s="9"/>
-      <c r="S34" s="9"/>
+      <c r="O34" s="9"/>
+      <c r="Q34" s="9"/>
       <c r="T34" s="9"/>
       <c r="U34" s="9"/>
-      <c r="W34" s="9"/>
+      <c r="V34" s="9"/>
       <c r="X34" s="9"/>
       <c r="Y34" s="9"/>
-      <c r="AA34" s="9">
+      <c r="Z34" s="9"/>
+      <c r="AB34" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="14">
+    <row r="35" spans="1:28" ht="14">
       <c r="A35">
         <v>29</v>
       </c>
@@ -23026,27 +23187,32 @@
       <c r="D35" s="29">
         <v>31963201</v>
       </c>
-      <c r="E35" s="9"/>
+      <c r="E35" s="29" t="inlineStr">
+        <is>
+          <t>20241110508</t>
+        </is>
+      </c>
       <c r="F35" s="9"/>
-      <c r="J35" s="9">
+      <c r="G35" s="9"/>
+      <c r="K35" s="9">
         <v>1</v>
       </c>
-      <c r="K35" s="9"/>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
-      <c r="P35" s="9">
+      <c r="O35" s="9"/>
+      <c r="Q35" s="9">
         <v>1</v>
       </c>
-      <c r="S35" s="9"/>
       <c r="T35" s="9"/>
       <c r="U35" s="9"/>
-      <c r="W35" s="9"/>
+      <c r="V35" s="9"/>
       <c r="X35" s="9"/>
       <c r="Y35" s="9"/>
-      <c r="AA35" s="9"/>
-    </row>
-    <row r="36" spans="1:27">
+      <c r="Z35" s="9"/>
+      <c r="AB35" s="9"/>
+    </row>
+    <row r="36" spans="1:28">
       <c r="A36">
         <v>30</v>
       </c>
@@ -23059,64 +23225,70 @@
       <c r="D36" s="31">
         <v>31985260</v>
       </c>
-      <c r="E36" s="33"/>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>20251110299</t>
+        </is>
+      </c>
       <c r="F36" s="33"/>
-      <c r="J36" s="9"/>
+      <c r="G36" s="33"/>
       <c r="K36" s="9"/>
-      <c r="L36" s="9">
+      <c r="L36" s="9"/>
+      <c r="M36" s="9">
         <v>2</v>
       </c>
-      <c r="M36" s="9"/>
       <c r="N36" s="9"/>
-      <c r="P36" s="9">
+      <c r="O36" s="9"/>
+      <c r="Q36" s="9">
         <v>1</v>
       </c>
-      <c r="S36" s="9"/>
-      <c r="T36" s="9">
+      <c r="T36" s="9"/>
+      <c r="U36" s="9">
         <v>2</v>
       </c>
-      <c r="U36" s="9">
+      <c r="V36" s="9">
         <v>4</v>
       </c>
-      <c r="W36" s="9">
+      <c r="X36" s="9">
         <v>4</v>
       </c>
-      <c r="X36" s="9">
+      <c r="Y36" s="9">
         <v>5</v>
       </c>
-      <c r="Y36" s="9">
+      <c r="Z36" s="9">
         <v>1</v>
       </c>
-      <c r="AA36" s="9">
+      <c r="AB36" s="9">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:27">
-      <c r="E37" s="28"/>
+    <row r="37" spans="1:28">
       <c r="F37" s="28"/>
-    </row>
-    <row r="38" spans="1:27">
-      <c r="E38" s="28"/>
+      <c r="G37" s="28"/>
+    </row>
+    <row r="38" spans="1:28">
       <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
+    <mergeCell ref="AB5:AC5"/>
+    <mergeCell ref="R5:S5"/>
+    <mergeCell ref="T5:U5"/>
+    <mergeCell ref="V5:W5"/>
+    <mergeCell ref="X5:Y5"/>
+    <mergeCell ref="Z5:AA5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="L5:M5"/>
+    <mergeCell ref="N5:O5"/>
+    <mergeCell ref="P5:Q5"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="C5:C6"/>
     <mergeCell ref="D5:D6"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:L5"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="O5:P5"/>
-    <mergeCell ref="AA5:AB5"/>
-    <mergeCell ref="Q5:R5"/>
-    <mergeCell ref="S5:T5"/>
-    <mergeCell ref="U5:V5"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Y5:Z5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="E5:E6"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datos Tesis Upstream/Estructura de Datos/2526-1/Participaciones Estructura de Datos 2526-1.xlsx
+++ b/Datos Tesis Upstream/Estructura de Datos/2526-1/Participaciones Estructura de Datos 2526-1.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
     <sheet name="Totales" sheetId="2" r:id="rId2"/>
     <sheet name="Estandar" sheetId="3" r:id="rId3"/>
+    <sheet name="Cronograma" sheetId="4" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -22676,70 +22677,86 @@
       <c r="Z21" s="9"/>
       <c r="AB21" s="9"/>
     </row>
-    <row r="22" spans="1:28" ht="14">
+    <row r="22" spans="1:28">
       <c r="A22">
         <v>16</v>
       </c>
-      <c r="B22" s="30" t="s">
+      <c r="B22" s="31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="31">
+        <v>31985260</v>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>20251110299</t>
+        </is>
+      </c>
+      <c r="F22" s="33"/>
+      <c r="G22" s="33"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
+      <c r="M22" s="9">
+        <v>2</v>
+      </c>
+      <c r="N22" s="9"/>
+      <c r="O22" s="9"/>
+      <c r="Q22" s="9">
+        <v>1</v>
+      </c>
+      <c r="T22" s="9"/>
+      <c r="U22" s="9">
+        <v>2</v>
+      </c>
+      <c r="V22" s="9">
+        <v>4</v>
+      </c>
+      <c r="X22" s="9">
+        <v>4</v>
+      </c>
+      <c r="Y22" s="9">
+        <v>5</v>
+      </c>
+      <c r="Z22" s="9">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" ht="14">
+      <c r="A23">
+        <v>17</v>
+      </c>
+      <c r="B23" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="30" t="s">
+      <c r="C23" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D23" s="30">
         <v>31229787</v>
       </c>
-      <c r="E22" s="30" t="inlineStr">
+      <c r="E23" s="30" t="inlineStr">
         <is>
           <t>20241110455</t>
         </is>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9">
+      <c r="F23" s="9"/>
+      <c r="G23" s="9">
         <v>1</v>
       </c>
-      <c r="K22" s="9">
+      <c r="K23" s="9">
         <v>1</v>
       </c>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9">
-        <v>3</v>
-      </c>
-      <c r="O22" s="9"/>
-      <c r="Q22" s="9"/>
-      <c r="T22" s="9"/>
-      <c r="U22" s="9"/>
-      <c r="V22" s="9"/>
-      <c r="X22" s="9"/>
-      <c r="Y22" s="9"/>
-      <c r="Z22" s="9"/>
-      <c r="AB22" s="9"/>
-    </row>
-    <row r="23" spans="1:28" ht="14">
-      <c r="A23">
-        <v>17</v>
-      </c>
-      <c r="B23" s="29" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>64</v>
-      </c>
-      <c r="D23" s="29">
-        <v>30719195</v>
-      </c>
-      <c r="E23" s="29" t="inlineStr">
-        <is>
-          <t>20231110418</t>
-        </is>
-      </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="K23" s="9"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
+      <c r="N23" s="9">
+        <v>3</v>
+      </c>
       <c r="O23" s="9"/>
       <c r="Q23" s="9"/>
       <c r="T23" s="9"/>
@@ -22754,18 +22771,18 @@
       <c r="A24">
         <v>18</v>
       </c>
-      <c r="B24" s="30" t="s">
-        <v>65</v>
-      </c>
-      <c r="C24" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="D24" s="30">
-        <v>31785756</v>
-      </c>
-      <c r="E24" s="30" t="inlineStr">
+      <c r="B24" s="29" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="29" t="s">
+        <v>64</v>
+      </c>
+      <c r="D24" s="29">
+        <v>30719195</v>
+      </c>
+      <c r="E24" s="29" t="inlineStr">
         <is>
-          <t>20241130167</t>
+          <t>20231110418</t>
         </is>
       </c>
       <c r="F24" s="9"/>
@@ -22788,18 +22805,18 @@
       <c r="A25">
         <v>19</v>
       </c>
-      <c r="B25" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="29" t="s">
-        <v>69</v>
-      </c>
-      <c r="D25" s="29">
-        <v>31020400</v>
-      </c>
-      <c r="E25" s="29" t="inlineStr">
+      <c r="B25" s="30" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="30">
+        <v>31785756</v>
+      </c>
+      <c r="E25" s="30" t="inlineStr">
         <is>
-          <t>20231130043</t>
+          <t>20241130167</t>
         </is>
       </c>
       <c r="F25" s="9"/>
@@ -22822,18 +22839,18 @@
       <c r="A26">
         <v>20</v>
       </c>
-      <c r="B26" s="30" t="s">
-        <v>70</v>
-      </c>
-      <c r="C26" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" s="30">
-        <v>29611077</v>
-      </c>
-      <c r="E26" s="30" t="inlineStr">
+      <c r="B26" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="29" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="29">
+        <v>31020400</v>
+      </c>
+      <c r="E26" s="29" t="inlineStr">
         <is>
-          <t>20221110015</t>
+          <t>20231130043</t>
         </is>
       </c>
       <c r="F26" s="9"/>
@@ -22856,24 +22873,22 @@
       <c r="A27">
         <v>21</v>
       </c>
-      <c r="B27" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="C27" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="29">
-        <v>31587327</v>
-      </c>
-      <c r="E27" s="29" t="inlineStr">
+      <c r="B27" s="30" t="s">
+        <v>70</v>
+      </c>
+      <c r="C27" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="D27" s="30">
+        <v>29611077</v>
+      </c>
+      <c r="E27" s="30" t="inlineStr">
         <is>
-          <t>20241130168</t>
+          <t>20221110015</t>
         </is>
       </c>
       <c r="F27" s="9"/>
-      <c r="G27" s="9">
-        <v>1</v>
-      </c>
+      <c r="G27" s="9"/>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
@@ -22892,27 +22907,27 @@
       <c r="A28">
         <v>22</v>
       </c>
-      <c r="B28" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="C28" s="30" t="s">
-        <v>76</v>
-      </c>
-      <c r="D28" s="30">
-        <v>30229939</v>
-      </c>
-      <c r="E28" s="30" t="inlineStr">
+      <c r="B28" s="29" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="D28" s="29">
+        <v>31587327</v>
+      </c>
+      <c r="E28" s="29" t="inlineStr">
         <is>
-          <t>20221120020</t>
+          <t>20241130168</t>
         </is>
       </c>
       <c r="F28" s="9"/>
-      <c r="G28" s="9"/>
+      <c r="G28" s="9">
+        <v>1</v>
+      </c>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
-      <c r="M28" s="9">
-        <v>4</v>
-      </c>
+      <c r="M28" s="9"/>
       <c r="N28" s="9"/>
       <c r="O28" s="9"/>
       <c r="Q28" s="9"/>
@@ -22928,120 +22943,116 @@
       <c r="A29">
         <v>23</v>
       </c>
-      <c r="B29" s="29" t="s">
+      <c r="B29" s="30" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D29" s="30">
+        <v>30229939</v>
+      </c>
+      <c r="E29" s="30" t="inlineStr">
+        <is>
+          <t>20221120020</t>
+        </is>
+      </c>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+      <c r="M29" s="9">
+        <v>4</v>
+      </c>
+      <c r="N29" s="9"/>
+      <c r="O29" s="9"/>
+      <c r="Q29" s="9"/>
+      <c r="T29" s="9"/>
+      <c r="U29" s="9"/>
+      <c r="V29" s="9"/>
+      <c r="X29" s="9"/>
+      <c r="Y29" s="9"/>
+      <c r="Z29" s="9"/>
+      <c r="AB29" s="9"/>
+    </row>
+    <row r="30" spans="1:28" ht="14">
+      <c r="A30">
+        <v>24</v>
+      </c>
+      <c r="B30" s="29" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="29" t="s">
+      <c r="C30" s="29" t="s">
         <v>79</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D30" s="29">
         <v>27985520</v>
       </c>
-      <c r="E29" s="29" t="inlineStr">
+      <c r="E30" s="29" t="inlineStr">
         <is>
           <t>20201110250</t>
         </is>
       </c>
-      <c r="F29" s="9">
+      <c r="F30" s="9">
         <v>1</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G30" s="9">
         <v>1</v>
       </c>
-      <c r="K29" s="9">
+      <c r="K30" s="9">
         <v>1</v>
       </c>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9">
+      <c r="L30" s="9"/>
+      <c r="M30" s="9"/>
+      <c r="N30" s="9">
         <v>8</v>
       </c>
-      <c r="O29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="T29" s="9">
+      <c r="O30" s="9"/>
+      <c r="Q30" s="9"/>
+      <c r="T30" s="9">
         <v>1</v>
       </c>
-      <c r="U29" s="9">
+      <c r="U30" s="9">
         <v>2</v>
       </c>
-      <c r="V29" s="9">
+      <c r="V30" s="9">
         <v>4</v>
       </c>
-      <c r="X29" s="9"/>
-      <c r="Y29" s="9">
+      <c r="X30" s="9"/>
+      <c r="Y30" s="9">
         <v>3</v>
       </c>
-      <c r="Z29" s="9">
+      <c r="Z30" s="9">
         <v>1</v>
       </c>
-      <c r="AB29" s="9">
+      <c r="AB30" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:28" ht="14">
-      <c r="A30">
-        <v>24</v>
-      </c>
-      <c r="B30" s="30" t="s">
+    <row r="31" spans="1:28" ht="14">
+      <c r="A31">
+        <v>25</v>
+      </c>
+      <c r="B31" s="30" t="s">
         <v>81</v>
       </c>
-      <c r="C30" s="30" t="s">
+      <c r="C31" s="30" t="s">
         <v>82</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D31" s="30">
         <v>31623487</v>
       </c>
-      <c r="E30" s="30" t="inlineStr">
+      <c r="E31" s="30" t="inlineStr">
         <is>
           <t>20231110186</t>
         </is>
       </c>
-      <c r="F30" s="9"/>
-      <c r="G30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="T30" s="9"/>
-      <c r="U30" s="9"/>
-      <c r="V30" s="9"/>
-      <c r="X30" s="9"/>
-      <c r="Y30" s="9"/>
-      <c r="Z30" s="9"/>
-      <c r="AB30" s="9"/>
-    </row>
-    <row r="31" spans="1:28" ht="14">
-      <c r="A31">
-        <v>25</v>
-      </c>
-      <c r="B31" s="29" t="s">
-        <v>83</v>
-      </c>
-      <c r="C31" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" s="29">
-        <v>27714324</v>
-      </c>
-      <c r="E31" s="29" t="inlineStr">
-        <is>
-          <t>20241130162</t>
-        </is>
-      </c>
-      <c r="F31" s="9">
-        <v>2</v>
-      </c>
-      <c r="G31" s="9">
-        <v>1</v>
-      </c>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
       <c r="M31" s="9"/>
-      <c r="N31" s="9">
-        <v>3</v>
-      </c>
+      <c r="N31" s="9"/>
       <c r="O31" s="9"/>
       <c r="Q31" s="9"/>
       <c r="T31" s="9"/>
@@ -23056,43 +23067,37 @@
       <c r="A32">
         <v>26</v>
       </c>
-      <c r="B32" s="30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C32" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="30">
-        <v>32001374</v>
-      </c>
-      <c r="E32" s="30" t="inlineStr">
+      <c r="B32" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C32" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D32" s="29">
+        <v>27714324</v>
+      </c>
+      <c r="E32" s="29" t="inlineStr">
         <is>
-          <t>20251110189</t>
+          <t>20241130162</t>
         </is>
       </c>
-      <c r="F32" s="9"/>
+      <c r="F32" s="9">
+        <v>2</v>
+      </c>
       <c r="G32" s="9">
-        <v>2</v>
-      </c>
-      <c r="K32" s="9">
         <v>1</v>
       </c>
+      <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-      <c r="O32" s="9">
-        <v>5</v>
-      </c>
-      <c r="Q32" s="9">
-        <v>1</v>
-      </c>
-      <c r="T32" s="9">
-        <v>1</v>
-      </c>
+      <c r="N32" s="9">
+        <v>3</v>
+      </c>
+      <c r="O32" s="9"/>
+      <c r="Q32" s="9"/>
+      <c r="T32" s="9"/>
       <c r="U32" s="9"/>
-      <c r="V32" s="9">
-        <v>4</v>
-      </c>
+      <c r="V32" s="9"/>
       <c r="X32" s="9"/>
       <c r="Y32" s="9"/>
       <c r="Z32" s="9"/>
@@ -23102,35 +23107,43 @@
       <c r="A33">
         <v>27</v>
       </c>
-      <c r="B33" s="29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C33" s="29" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="29">
-        <v>30394855</v>
-      </c>
-      <c r="E33" s="29" t="inlineStr">
+      <c r="B33" s="30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C33" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D33" s="30">
+        <v>32001374</v>
+      </c>
+      <c r="E33" s="30" t="inlineStr">
         <is>
-          <t>20241110467</t>
+          <t>20251110189</t>
         </is>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="9"/>
+      <c r="G33" s="9">
+        <v>2</v>
+      </c>
+      <c r="K33" s="9">
         <v>1</v>
       </c>
-      <c r="G33" s="9">
-        <v>1</v>
-      </c>
-      <c r="K33" s="9"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
-      <c r="O33" s="9"/>
-      <c r="Q33" s="9"/>
-      <c r="T33" s="9"/>
+      <c r="O33" s="9">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="9">
+        <v>1</v>
+      </c>
+      <c r="T33" s="9">
+        <v>1</v>
+      </c>
       <c r="U33" s="9"/>
-      <c r="V33" s="9"/>
+      <c r="V33" s="9">
+        <v>4</v>
+      </c>
       <c r="X33" s="9"/>
       <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
@@ -23140,24 +23153,26 @@
       <c r="A34">
         <v>28</v>
       </c>
-      <c r="B34" s="30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>92</v>
-      </c>
-      <c r="D34" s="30">
-        <v>31872806</v>
-      </c>
-      <c r="E34" s="30" t="inlineStr">
+      <c r="B34" s="29" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="D34" s="29">
+        <v>30394855</v>
+      </c>
+      <c r="E34" s="29" t="inlineStr">
         <is>
-          <t>20251110273</t>
+          <t>20241110467</t>
         </is>
       </c>
       <c r="F34" s="9">
         <v>1</v>
       </c>
-      <c r="G34" s="9"/>
+      <c r="G34" s="9">
+        <v>1</v>
+      </c>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
@@ -23170,97 +23185,83 @@
       <c r="X34" s="9"/>
       <c r="Y34" s="9"/>
       <c r="Z34" s="9"/>
-      <c r="AB34" s="9">
-        <v>1</v>
-      </c>
+      <c r="AB34" s="9"/>
     </row>
     <row r="35" spans="1:28" ht="14">
       <c r="A35">
         <v>29</v>
       </c>
-      <c r="B35" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="C35" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="D35" s="29">
-        <v>31963201</v>
-      </c>
-      <c r="E35" s="29" t="inlineStr">
+      <c r="B35" s="30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C35" s="30" t="s">
+        <v>92</v>
+      </c>
+      <c r="D35" s="30">
+        <v>31872806</v>
+      </c>
+      <c r="E35" s="30" t="inlineStr">
         <is>
-          <t>20241110508</t>
+          <t>20251110273</t>
         </is>
       </c>
-      <c r="F35" s="9"/>
+      <c r="F35" s="9">
+        <v>1</v>
+      </c>
       <c r="G35" s="9"/>
-      <c r="K35" s="9">
-        <v>1</v>
-      </c>
+      <c r="K35" s="9"/>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
       <c r="O35" s="9"/>
-      <c r="Q35" s="9">
-        <v>1</v>
-      </c>
+      <c r="Q35" s="9"/>
       <c r="T35" s="9"/>
       <c r="U35" s="9"/>
       <c r="V35" s="9"/>
       <c r="X35" s="9"/>
       <c r="Y35" s="9"/>
       <c r="Z35" s="9"/>
-      <c r="AB35" s="9"/>
-    </row>
-    <row r="36" spans="1:28">
+      <c r="AB35" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" ht="14">
       <c r="A36">
         <v>30</v>
       </c>
-      <c r="B36" s="31" t="s">
-        <v>96</v>
-      </c>
-      <c r="C36" s="31" t="s">
-        <v>97</v>
-      </c>
-      <c r="D36" s="31">
-        <v>31985260</v>
-      </c>
-      <c r="E36" s="31" t="inlineStr">
+      <c r="B36" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="29" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="29">
+        <v>31963201</v>
+      </c>
+      <c r="E36" s="29" t="inlineStr">
         <is>
-          <t>20251110299</t>
+          <t>20241110508</t>
         </is>
       </c>
-      <c r="F36" s="33"/>
-      <c r="G36" s="33"/>
-      <c r="K36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="K36" s="9">
+        <v>1</v>
+      </c>
       <c r="L36" s="9"/>
-      <c r="M36" s="9">
-        <v>2</v>
-      </c>
+      <c r="M36" s="9"/>
       <c r="N36" s="9"/>
       <c r="O36" s="9"/>
       <c r="Q36" s="9">
         <v>1</v>
       </c>
       <c r="T36" s="9"/>
-      <c r="U36" s="9">
-        <v>2</v>
-      </c>
-      <c r="V36" s="9">
-        <v>4</v>
-      </c>
-      <c r="X36" s="9">
-        <v>4</v>
-      </c>
-      <c r="Y36" s="9">
-        <v>5</v>
-      </c>
-      <c r="Z36" s="9">
-        <v>1</v>
-      </c>
-      <c r="AB36" s="9">
-        <v>2</v>
-      </c>
+      <c r="U36" s="9"/>
+      <c r="V36" s="9"/>
+      <c r="X36" s="9"/>
+      <c r="Y36" s="9"/>
+      <c r="Z36" s="9"/>
+      <c r="AB36" s="9"/>
     </row>
     <row r="37" spans="1:28">
       <c r="F37" s="28"/>
@@ -23294,4 +23295,335 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">semana</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">dia_sesion</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tipo_sesion</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>5</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>5</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>6</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>7</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>7</v>
+      </c>
+      <c r="B15">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>0</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>8</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>8</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>9</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>9</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>10</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>10</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>12</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>12</v>
+      </c>
+      <c r="B25">
+        <v>2</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">evaluacion</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nota:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tema = código del catálogo de la asignatura. Si la sesión no cubre contenido nuevo: tema = 0 y tipo_sesion indica la causa (evaluacion, repaso, sin_clase, administrativa). Si tema &gt; 0 la sesión es de contenido y tipo_sesion queda vacío.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>